--- a/Results/tablolar_tumu.xlsx
+++ b/Results/tablolar_tumu.xlsx
@@ -26,12 +26,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TableS13" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TableS14" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TableS15" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TableS16" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ek_H3_ham_oranlar" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TableS17" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TableS18" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TableS19" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TableS20" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ek_ulusal_karsilik" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TableS16" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ek_H3_ham_oranlar" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TableS17" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TableS18" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TableS19" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TableS20" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ek_tasarim_etkisi" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -532,7 +534,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 1. Characteristics of households and adults by food insecurity and income poverty, Turkey, 2025.</t>
+          <t>Table 1. Characteristics of households and adults by meal-affordability deprivation and income poverty, Türkiye, 2025.</t>
         </is>
       </c>
     </row>
@@ -545,12 +547,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Food secure</t>
+          <t>Not meal-deprived</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Food insecure</t>
+          <t>Meal-deprived</t>
         </is>
       </c>
       <c r="D3" s="11" t="n"/>
@@ -2123,7 +2125,7 @@
     <row r="82">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>Food insecure: household cannot afford a meal with meat, chicken or fish every second day (HE090). Poor: equivalized disposable income below 60% of the national median.</t>
+          <t>Meal-deprived: household cannot afford a meal with meat, chicken or fish, or a vegetarian equivalent, every second day (HE090 = 2). Poor: equivalized disposable income below 60% of the national median.</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2171,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table S5. Model specification and diagnostics for the dietary and health-cost comparisons (H3), 2025.</t>
+          <t>Table S5. Model specification and diagnostics for the consumption-frequency and health-cost comparisons (H3), 2025.</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2407,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>C2: G2 vs G3 (food insecure)</t>
+          <t>C2: G2 vs G3 (meal-deprived)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -2462,7 +2464,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>C2: G2 vs G3 (food insecure)</t>
+          <t>C2: G2 vs G3 (meal-deprived)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -2519,7 +2521,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>C2: G2 vs G3 (food insecure)</t>
+          <t>C2: G2 vs G3 (meal-deprived)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -2633,7 +2635,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>C2: G2 vs G3 (food insecure)</t>
+          <t>C2: G2 vs G3 (meal-deprived)</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -2783,7 +2785,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Small LightGBM fitted to 2024–2025 food insecurity; shared household random effect for matched 2024–2025 pairs; intercept recalibrated to the observed prevalence</t>
+          <t>Small LightGBM fitted to 2024–2025 meal-affordability deprivation; shared household random effect for matched 2024–2025 pairs; intercept recalibrated to the observed prevalence</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -2810,12 +2812,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Design A: true status assigned from observed HE090 by Bayes' rule within cells of equivalized income quintile × poverty status, using each cell's observed prevalence; design B: the same Se and Sp for every household, true status assigned from the recalibrated out-of-time LightGBM probability of reporting food insecurity; differential: Sp 5 pp lower in income quintiles 1–2</t>
+          <t>Design A: true status assigned from observed HE090 by Bayes' rule within cells of equivalized income quintile × poverty status, using each cell's observed prevalence; design B: the same Se and Sp for every household, true status assigned from the recalibrated out-of-time LightGBM probability of reporting meal-affordability deprivation; differential: Sp 5 pp lower in income quintiles 1–2</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Exclusion error (simulated and closed form), food insecurity among the poor, rule-set, LightGBM and poverty-line sensitivity recomputed with assigned true status; realized Se and Sp by decile of LightGBM risk</t>
+          <t>Exclusion error (simulated and closed form), meal-affordability deprivation among the poor, rule-set, LightGBM and poverty-line sensitivity recomputed with assigned true status; realized Se and Sp by decile of LightGBM risk</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="48.71" customWidth="1" min="1" max="1"/>
@@ -2879,7 +2881,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table S7. Food insecurity and exclusion error of the 60% poverty line by household characteristics, 2025.</t>
+          <t>Table S7. Meal-affordability deprivation and exclusion error of the 60% poverty line by household characteristics, 2025.</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2899,7 @@
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>Food insecure, % (95% CI)</t>
+          <t>Meal-deprived, % (95% CI)</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
@@ -4407,46 +4409,526 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="inlineStr">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>Southeast Anatolia</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>2,735</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>52.8 (50.6, 55.0)</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>34.9 (32.1, 37.7)</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E54" s="4" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F54" s="4" t="inlineStr">
         <is>
           <t>26.4</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="inlineStr">
-        <is>
-          <t>n, unweighted number of households; percentages and prevalences weighted. Exclusion error: % of food-insecure households not poor. Share of missed households: distribution of food-insecure, non-poor households across categories.</t>
-        </is>
-      </c>
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Change in main activity since the income reference year</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr"/>
+      <c r="C55" s="4" t="inlineStr"/>
+      <c r="D55" s="4" t="inlineStr"/>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="9" t="inlineStr">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>An adult stopped working, none started</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>1,476</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>31.8 (29.0, 34.6)</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>70.9 (66.4, 75.4)</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>59.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>An adult started working, none stopped</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>1,921</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>41.8 (39.2, 44.3)</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>53.0 (49.2, 56.9)</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>43.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>Both changes</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>36.0 (27.1, 44.9)</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>72.5 (59.9, 85.2)</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>65.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>22,197</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>36.9 (36.1, 37.6)</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>69.5 (68.4, 70.6)</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>86.6</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>59.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>Not determined (adult without individual record)</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>39.3 (27.8, 50.8)</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="9"/>
+            </rPr>
+            <t>61.4 (43.9, 78.9)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="9"/>
+              <vertAlign val="superscript"/>
+            </rPr>
+            <t>a</t>
+          </r>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>60.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Ability to make ends meet</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr"/>
+      <c r="C61" s="4" t="inlineStr"/>
+      <c r="D61" s="4" t="inlineStr"/>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>With great difficulty</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>1,234</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>76.4 (73.5, 79.3)</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>51.3 (47.5, 55.0)</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>With difficulty</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>6,981</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>55.6 (54.2, 56.9)</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>63.6 (61.9, 65.4)</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>36.8</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>52.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>With some difficulty</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>11,545</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>33.9 (32.9, 34.9)</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>72.8 (71.3, 74.3)</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>43.9</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>Fairly easily or more easily</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>6,076</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>14.5 (13.5, 15.5)</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>84.0 (81.5, 86.5)</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>11.7</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>74.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Other deprivation items (of 12)</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr"/>
+      <c r="C66" s="4" t="inlineStr"/>
+      <c r="D66" s="4" t="inlineStr"/>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>10,194</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>1.6 (1.4, 1.9)</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>93.6 (89.2, 97.9)</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>1–2</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>6,402</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>34.1 (32.7, 35.5)</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>84.6 (82.9, 86.3)</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>29.1</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>79.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>3–4</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>4,010</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>75.6 (74.0, 77.2)</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>73.8 (72.1, 75.6)</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>33.1</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>65.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>≥5</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>5,230</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>92.1 (91.2, 93.0)</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>54.3 (52.6, 56.0)</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>35.2</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>n, unweighted number of households; percentages and prevalences weighted. Exclusion error: % of meal-deprived households not poor. Share of missed households: distribution of meal-deprived, non-poor households across categories.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>Change in main activity: adults aged ≥18 with an individual record; worked mainly in the income reference year, at least 7 months in full- or part-time work (FI260 + FI270); working at the interview, current activity status employed (FI010 1–4). Households with an adult without an individual record are not classified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>Ability to make ends meet: HE040. Other deprivation items: number of the 12 Eurostat material and social deprivation items other than the meal item that the household (reference person for personal items) lacks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4461,7 +4943,7 @@
               <rFont val="Times New Roman"/>
               <sz val="8"/>
             </rPr>
-            <t xml:space="preserve"> 20–50 food-insecure households in the cell; –, fewer than 20 (not shown). </t>
+            <t xml:space="preserve"> 20–50 meal-deprived households in the cell; –, fewer than 20 (not shown). </t>
           </r>
           <r>
             <rPr>
@@ -4493,7 +4975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F161"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="48.71" customWidth="1" min="1" max="1"/>
@@ -4507,7 +4989,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table S8. Exclusion error of the 60% poverty line: sensitivity to the TR63 region and to the variance estimator, and income-related concentration of food insecurity.</t>
+          <t>Table S8. Exclusion error of the 60% poverty line: sensitivity analyses, income-gradient estimates and income-related concentration of meal-affordability deprivation.</t>
         </is>
       </c>
     </row>
@@ -4545,535 +5027,4748 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Exclusion error by year, and year differences assuming independent samples</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Households</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>70.4 (69.3, 71.4)</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>70.4 (69.3, 71.4)</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>70.4 (69.4, 71.4)</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>70.4 (68.9, 71.9)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Households</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>70.3 (69.3, 71.4)</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>70.9 (69.8, 71.9)</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>70.3 (69.3, 71.3)</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>70.3 (68.9, 71.8)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Households</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>68.1 (67.0, 69.1)</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>68.8 (67.7, 69.8)</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>68.1 (67.1, 69.1)</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>68.1 (66.6, 69.6)</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Persons</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>63.3 (61.9, 64.7)</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>63.3 (61.9, 64.7)</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>63.3 (62.0, 64.7)</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>63.3 (61.4, 65.3)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Persons</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>63.2 (61.8, 64.5)</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>63.7 (62.3, 65.1)</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>63.2 (61.8, 64.5)</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>63.2 (61.2, 65.1)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Persons</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>57.6 (56.3, 59.0)</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>58.2 (56.8, 59.6)</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>57.6 (56.3, 59.0)</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>57.6 (55.7, 59.6)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Households</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>2025 − 2023</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>−2.3 (−3.8, −0.8)</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>−1.6 (−3.1, −0.1)</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>−2.3 (−3.7, −0.9)</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>−2.3 (−4.4, −0.2)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Households</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>2024 − 2023</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>−0.1 (−1.5, 1.4)</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>0.5 (−1.0, 1.9)</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>−0.1 (−1.5, 1.4)</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>−0.1 (−2.1, 2.0)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Households</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>2025 − 2024</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>−2.2 (−3.7, −0.8)</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>−2.1 (−3.6, −0.6)</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>−2.2 (−3.7, −0.8)</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>−2.2 (−4.3, −0.2)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Persons</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>2025 − 2023</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>−5.7 (−7.6, −3.7)</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>−5.1 (−7.1, −3.1)</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>−5.7 (−7.6, −3.8)</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>−5.7 (−8.4, −2.9)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Persons</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>2024 − 2023</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>−0.2 (−2.1, 1.8)</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>0.4 (−1.6, 2.4)</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>−0.2 (−2.1, 1.8)</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>−0.2 (−2.9, 2.6)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>Persons</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>2025 − 2024</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>−5.5 (−7.5, −3.6)</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>−5.5 (−7.5, −3.5)</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>−5.5 (−7.4, −3.6)</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>−5.5 (−8.3, −2.8)</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Erreygers index (persons)</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>−0.485 (−0.500, −0.469)</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>−0.485 (−0.507, −0.463)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Erreygers index (persons)</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>−0.483 (−0.499, −0.467)</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>−0.483 (−0.506, −0.461)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Erreygers index (persons)</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>−0.577 (−0.591, −0.563)</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>−0.577 (−0.597, −0.557)</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>Erreygers index (persons)</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>2025 − 2023</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>−0.092 (−0.113, −0.071)</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>−0.092 (−0.122, −0.062)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>Exclusion error, % of food-insecure households (persons) not poor (95% CI). TR63 (Hatay, Kahramanmaraş, Osmaniye) has no households in 2023. Pseudo-strata: NUTS 2 regions used as strata in the linearization variance.</t>
-        </is>
-      </c>
-    </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>Design effect 2: intervals with the variance doubled, as a stand-in for the area-level clustering of the survey sample, which is not identified in the files.</t>
-        </is>
-      </c>
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Year differences with households matched across survey years as clusters</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr"/>
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>Erreygers concentration index of food insecurity by equivalized-income rank (persons, FK050); negative values indicate concentration among lower-income persons. Differences assume independent samples. –, not computed.</t>
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Exclusion error, households</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2023</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>−2.3 (−3.7, −0.9)</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>−1.6 (−3.0, −0.2)</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>−2.3 (−4.2, −0.4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Exclusion error, households</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>2024 − 2023</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>−0.1 (−1.3, 1.1)</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>0.5 (−0.7, 1.7)</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>−0.1 (−1.8, 1.6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Exclusion error, households</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2024</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>−2.2 (−3.4, −1.1)</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>−2.1 (−3.3, −0.9)</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>−2.2 (−3.9, −0.6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Exclusion error, persons</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2023</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>−5.7 (−7.5, −3.8)</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>−5.1 (−6.9, −3.3)</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>−5.7 (−8.2, −3.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Exclusion error, persons</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>2024 − 2023</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>−0.2 (−1.8, 1.5)</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>0.4 (−1.2, 2.0)</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>−0.2 (−2.4, 2.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Exclusion error, persons</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2024</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>−5.5 (−7.1, −3.9)</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>−5.5 (−7.1, −3.9)</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>−5.5 (−7.8, −3.3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Meal-affordability deprivation, households</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2023</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>−0.4 (−1.3, 0.5)</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>−1.1 (−1.9, −0.2)</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>−0.4 (−1.6, 0.8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Meal-affordability deprivation, persons</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2023</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>−4.1 (−5.1, −3.0)</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>−4.7 (−5.7, −3.6)</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>−4.1 (−5.5, −2.6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Erreygers index (persons)</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2023</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>−0.092 (−0.112, −0.072)</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>−0.092 (−0.120, −0.064)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Income gradient of meal-affordability deprivation: Wald tests, F (p)</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr"/>
+      <c r="C31" s="4" t="inlineStr"/>
+      <c r="D31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Association with log relative income (4 df)</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>578.1 (p &lt; 0.001)</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>289.0 (p &lt; 0.001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Association with log relative income (4 df)</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>623.5 (p &lt; 0.001)</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>311.8 (p &lt; 0.001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Association with log relative income (4 df)</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>717.6 (p &lt; 0.001)</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>358.8 (p &lt; 0.001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Departure from linearity (3 df)</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>23.6 (p &lt; 0.001)</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>11.8 (p &lt; 0.001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Departure from linearity (3 df)</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>17.2 (p &lt; 0.001)</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>8.6 (p &lt; 0.001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Departure from linearity (3 df)</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>48.4 (p &lt; 0.001)</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>24.2 (p &lt; 0.001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Equality of the two curves (5 df)</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>2023 and 2025</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>33.5 (p &lt; 0.001)</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>16.8 (p &lt; 0.001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Equality of the two curves (5 df)</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>2023 and 2024</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>0.9 (p = 0.473)</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>0.5 (p = 0.810)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>Equality of the two curves (5 df)</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>2024 and 2025</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>38.5 (p &lt; 0.001)</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>19.2 (p &lt; 0.001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Equality of the two curves (5 df), independent samples</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>2023 and 2025</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>30.4 (p &lt; 0.001)</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>15.2 (p &lt; 0.001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Equality of the two curves (5 df), independent samples</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>2023 and 2024</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>0.7 (p = 0.622)</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>0.4 (p = 0.882)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>Equality of the two curves (5 df), independent samples</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>2024 and 2025</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>29.9 (p &lt; 0.001)</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>14.9 (p &lt; 0.001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Equality of curve shape (4 df)</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>2023 and 2025</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>41.8 (p &lt; 0.001)</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>20.9 (p &lt; 0.001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Equality of curve shape (4 df)</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>2023 and 2024</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>0.8 (p = 0.530)</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>0.4 (p = 0.812)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>Equality of curve shape (4 df)</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>2024 and 2025</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>48.0 (p &lt; 0.001)</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>24.0 (p &lt; 0.001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>Equality of curve shape (4 df), independent samples</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>2023 and 2025</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>38.0 (p &lt; 0.001)</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>19.0 (p &lt; 0.001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>Equality of curve shape (4 df), independent samples</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>2023 and 2024</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>0.7 (p = 0.627)</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>0.3 (p = 0.861)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Equality of curve shape (4 df), independent samples</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>2024 and 2025</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>37.3 (p &lt; 0.001)</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>18.7 (p &lt; 0.001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>Equality of the three curves (10 df)</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>2023–2025</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>21.8 (p &lt; 0.001)</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>10.9 (p &lt; 0.001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>Equality of curve shape, three years (8 df)</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>2023–2025</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>27.1 (p &lt; 0.001)</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>13.5 (p &lt; 0.001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Predicted probability of meal-affordability deprivation at selected relative incomes, % (95% CI)</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr"/>
+      <c r="C52" s="4" t="inlineStr"/>
+      <c r="D52" s="4" t="inlineStr"/>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.3</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>73.4 (70.8, 76.0)</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.3</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>75.1 (72.5, 77.6)</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.3</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>80.8 (78.4, 83.1)</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.4</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>68.6 (67.0, 70.2)</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.4</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>70.0 (68.4, 71.5)</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.4</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>75.5 (73.9, 77.0)</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.5</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>64.3 (62.9, 65.7)</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.5</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>65.4 (64.0, 66.7)</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.5</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>70.4 (69.1, 71.7)</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.6</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>60.0 (58.5, 61.6)</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.6</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>60.8 (59.3, 62.3)</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.6</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>65.1 (63.7, 66.6)</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.8</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>51.0 (49.7, 52.2)</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.8</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>51.4 (50.2, 52.6)</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.8</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>53.3 (52.0, 54.5)</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 1.0</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>42.1 (40.5, 43.6)</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 1.0</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>42.2 (40.7, 43.7)</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 1.0</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>41.8 (40.2, 43.3)</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 1.25</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>32.7 (31.5, 33.9)</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 1.25</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>32.3 (31.2, 33.5)</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 1.25</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>30.2 (29.0, 31.4)</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 1.5</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>25.5 (24.2, 26.9)</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 1.5</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>25.1 (23.9, 26.4)</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 1.5</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>21.0 (19.6, 22.5)</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 2.0</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>16.3 (15.2, 17.5)</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 2.0</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>16.6 (15.5, 17.8)</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 2.0</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>9.1 (8.2, 10.0)</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 3.0</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>8.1 (7.0, 9.3)</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 3.0</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>9.2 (8.2, 10.4)</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 3.0</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>1.8 (1.3, 2.6)</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>Year differences in predicted probability at selected relative incomes, pp (95% CI), matched households as clusters</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr"/>
+      <c r="C83" s="4" t="inlineStr"/>
+      <c r="D83" s="4" t="inlineStr"/>
+      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.3</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2023</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>7.4 (4.1, 10.7)</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>6.9 (3.5, 10.3)</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>7.4 (2.7, 12.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.4</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2023</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>6.9 (4.8, 9.0)</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>6.3 (4.2, 8.4)</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>6.9 (3.9, 9.8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.5</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2023</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>6.1 (4.3, 7.9)</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>5.4 (3.6, 7.2)</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>6.1 (3.6, 8.6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.6</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2023</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>5.1 (3.1, 7.1)</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>4.4 (2.4, 6.4)</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>5.1 (2.3, 7.9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.8</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2023</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>2.3 (0.7, 3.9)</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>1.8 (0.2, 3.5)</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>2.3 (0.0, 4.6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 1.0</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2023</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>−0.3 (−2.4, 1.8)</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>−0.5 (−2.6, 1.6)</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>−0.3 (−3.2, 2.6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 1.25</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2023</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>−2.5 (−4.1, −0.8)</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>−2.5 (−4.2, −0.9)</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>−2.5 (−4.8, −0.2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 1.5</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2023</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>−4.5 (−6.4, −2.6)</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>−4.5 (−6.4, −2.6)</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>−4.5 (−7.2, −1.8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 2.0</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2023</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>−7.3 (−8.7, −5.9)</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>−7.2 (−8.6, −5.8)</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>−7.3 (−9.2, −5.3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 3.0</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2023</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>−6.2 (−7.6, −4.9)</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>−6.2 (−7.5, −4.8)</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>−6.2 (−8.1, −4.4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.3</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>2024 − 2023</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>1.7 (−1.5, 4.9)</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>1.0 (−2.3, 4.2)</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>1.7 (−2.8, 6.2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.4</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>2024 − 2023</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>1.4 (−0.6, 3.3)</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>0.6 (−1.3, 2.6)</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>1.4 (−1.4, 4.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.5</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>2024 − 2023</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>1.1 (−0.6, 2.7)</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>0.3 (−1.3, 2.0)</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>1.1 (−1.3, 3.4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.6</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>2024 − 2023</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>0.8 (−1.0, 2.6)</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>0.1 (−1.7, 1.9)</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>0.8 (−1.7, 3.3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.8</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>2024 − 2023</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>0.4 (−1.0, 1.8)</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>−0.3 (−1.7, 1.1)</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>0.4 (−1.6, 2.4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 1.0</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>2024 − 2023</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>0.1 (−1.7, 1.9)</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>−0.5 (−2.3, 1.4)</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>0.1 (−2.5, 2.7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 1.25</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>2024 − 2023</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>−0.3 (−1.7, 1.1)</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>−0.6 (−2.0, 0.8)</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>−0.3 (−2.3, 1.7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 1.5</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>2024 − 2023</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>−0.4 (−2.0, 1.3)</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>−0.4 (−2.1, 1.2)</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>−0.4 (−2.7, 2.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 2.0</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>2024 − 2023</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>0.3 (−1.1, 1.7)</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>0.2 (−1.2, 1.6)</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>0.3 (−1.7, 2.3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 3.0</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>2024 − 2023</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>1.1 (−0.4, 2.6)</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>0.9 (−0.6, 2.4)</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>1.1 (−1.0, 3.2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.3</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2024</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>5.7 (2.7, 8.7)</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>6.0 (2.8, 9.1)</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>5.7 (1.5, 9.9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.4</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2024</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>5.5 (3.7, 7.3)</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>5.7 (3.8, 7.5)</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>5.5 (3.0, 8.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.5</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2024</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>5.1 (3.6, 6.6)</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>5.1 (3.6, 6.7)</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>5.1 (2.9, 7.2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.6</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2024</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>4.3 (2.6, 6.0)</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>4.3 (2.6, 6.1)</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>4.3 (1.9, 6.7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.8</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2024</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>1.9 (0.5, 3.3)</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>2.1 (0.7, 3.5)</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>1.9 (−0.1, 3.8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 1.0</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2024</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>−0.4 (−2.2, 1.4)</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>0.0 (−1.9, 1.8)</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>−0.4 (−3.0, 2.2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 1.25</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2024</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>−2.2 (−3.6, −0.7)</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>−2.0 (−3.4, −0.5)</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>−2.2 (−4.2, −0.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 1.5</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2024</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>−4.1 (−5.9, −2.4)</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>−4.0 (−5.8, −2.3)</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>−4.1 (−6.6, −1.7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 2.0</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2024</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>−7.5 (−8.8, −6.3)</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>−7.4 (−8.7, −6.1)</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>−7.5 (−9.4, −5.7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 3.0</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2024</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>−7.4 (−8.6, −6.1)</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>−7.0 (−8.3, −5.8)</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>−7.4 (−9.1, −5.6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>Year differences in predicted probability, pp (95% CI), assuming independent samples</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr"/>
+      <c r="C114" s="4" t="inlineStr"/>
+      <c r="D114" s="4" t="inlineStr"/>
+      <c r="E114" s="4" t="inlineStr"/>
+      <c r="F114" s="4" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.3</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2023</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>7.4 (3.9, 10.9)</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.4</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2023</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>6.9 (4.7, 9.1)</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.5</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2023</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>6.1 (4.2, 8.0)</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.6</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2023</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>5.1 (3.0, 7.2)</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 0.8</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2023</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>2.3 (0.6, 4.1)</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 1.0</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2023</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>−0.3 (−2.5, 1.9)</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 1.25</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2023</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>−2.5 (−4.2, −0.7)</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 1.5</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2023</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>−4.5 (−6.5, −2.5)</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 2.0</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2023</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>−7.3 (−8.7, −5.8)</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="7" t="inlineStr">
+        <is>
+          <t>Relative income 3.0</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2023</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>−6.2 (−7.6, −4.9)</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>Number of spline knots: design-based AIC (difference from five knots), largest difference from the five-knot curve, and 2025 − 2023 differences</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr"/>
+      <c r="C125" s="4" t="inlineStr"/>
+      <c r="D125" s="4" t="inlineStr"/>
+      <c r="E125" s="4" t="inlineStr"/>
+      <c r="F125" s="4" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t>3 knots (0.1, 0.5, 0.9)</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>dAIC 1.7; largest difference 1.18 pp</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t>3 knots (0.1, 0.5, 0.9)</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>dAIC 12.5; largest difference 1.45 pp</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="7" t="inlineStr">
+        <is>
+          <t>3 knots (0.1, 0.5, 0.9)</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>dAIC 3.3; largest difference 1.12 pp</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>3 knots</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2023</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>0.6: 5.6 (4.3, 6.9); 2.0: −7.6 (−8.8, −6.4)</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t>4 knots (0.05, 0.35, 0.65, 0.95)</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>dAIC −2.5; largest difference 0.13 pp</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>4 knots (0.05, 0.35, 0.65, 0.95)</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>dAIC −2.2; largest difference 0.27 pp</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>4 knots (0.05, 0.35, 0.65, 0.95)</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>dAIC −0.5; largest difference 0.81 pp</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>4 knots</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2023</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>0.6: 4.6 (3.0, 6.2); 2.0: −7.5 (−8.7, −6.3)</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t>5 knots (0.05, 0.275, 0.5, 0.725, 0.95), main</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>dAIC 0.0; largest difference 0.00 pp</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>5 knots (0.05, 0.275, 0.5, 0.725, 0.95), main</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>dAIC 0.0; largest difference 0.00 pp</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="7" t="inlineStr">
+        <is>
+          <t>5 knots (0.05, 0.275, 0.5, 0.725, 0.95), main</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>dAIC 0.0; largest difference 0.00 pp</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="7" t="inlineStr">
+        <is>
+          <t>5 knots</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2023</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>0.6: 5.1 (3.1, 7.1); 2.0: −7.3 (−8.7, −5.9)</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t>6 knots (0.05, 0.23, 0.41, 0.59, 0.77, 0.95)</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>dAIC −6.2; largest difference 1.53 pp</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="7" t="inlineStr">
+        <is>
+          <t>6 knots (0.05, 0.23, 0.41, 0.59, 0.77, 0.95)</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>dAIC 0.8; largest difference 0.74 pp</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="7" t="inlineStr">
+        <is>
+          <t>6 knots (0.05, 0.23, 0.41, 0.59, 0.77, 0.95)</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>dAIC −1.6; largest difference 1.07 pp</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="7" t="inlineStr">
+        <is>
+          <t>6 knots</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2023</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>0.6: 4.9 (2.8, 7.0); 2.0: −6.9 (−8.5, −5.3)</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="7" t="inlineStr">
+        <is>
+          <t>7 knots (0.025, 0.1833, 0.3417, 0.5, 0.6583, 0.8167, 0.975)</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>dAIC −17.2; largest difference 2.29 pp</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="7" t="inlineStr">
+        <is>
+          <t>7 knots (0.025, 0.1833, 0.3417, 0.5, 0.6583, 0.8167, 0.975)</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>dAIC −6.5; largest difference 1.70 pp</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t>7 knots (0.025, 0.1833, 0.3417, 0.5, 0.6583, 0.8167, 0.975)</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>dAIC −3.5; largest difference 1.49 pp</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="7" t="inlineStr">
+        <is>
+          <t>7 knots</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>2025 − 2023</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>0.6: 4.9 (3.0, 6.8); 2.0: −6.9 (−8.7, −5.1)</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
+          <t>The 60% line in real terms</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr"/>
+      <c r="C146" s="4" t="inlineStr"/>
+      <c r="D146" s="4" t="inlineStr"/>
+      <c r="E146" s="4" t="inlineStr"/>
+      <c r="F146" s="4" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="7" t="inlineStr">
+        <is>
+          <t>60% line, TRY per equivalent adult per year, income-year prices</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>2023 (income 2022)</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>38,531</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="7" t="inlineStr">
+        <is>
+          <t>60% line at 2022 prices, TRY</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>2023 (income 2022)</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>38,531</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="7" t="inlineStr">
+        <is>
+          <t>Consumer price index, survey year / income year</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>2023 (income 2022)</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>1.539</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="7" t="inlineStr">
+        <is>
+          <t>60% line, TRY per equivalent adult per year, income-year prices</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>2024 (income 2023)</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>81,742</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="7" t="inlineStr">
+        <is>
+          <t>60% line at 2022 prices, TRY</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>2024 (income 2023)</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>53,128 (+37.9% from the previous survey)</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="7" t="inlineStr">
+        <is>
+          <t>Consumer price index, survey year / income year</t>
+        </is>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>2024 (income 2023)</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>1.585</t>
+        </is>
+      </c>
+      <c r="D152" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="7" t="inlineStr">
+        <is>
+          <t>60% line, TRY per equivalent adult per year, income-year prices</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>2025 (income 2024)</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>144,690</t>
+        </is>
+      </c>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="7" t="inlineStr">
+        <is>
+          <t>60% line at 2022 prices, TRY</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>2025 (income 2024)</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>59,329 (+11.7% from the previous survey)</t>
+        </is>
+      </c>
+      <c r="D154" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="8" t="inlineStr">
+        <is>
+          <t>Consumer price index, survey year / income year</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>2025 (income 2024)</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>1.349</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F155" s="5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="9" t="inlineStr">
+        <is>
+          <t>Exclusion error, % of meal-deprived households (persons) not poor (95% CI). TR63 (Hatay, Kahramanmaraş, Osmaniye) has no households in 2023. Pseudo-strata: NUTS 2 regions used as strata in the linearization variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="9" t="inlineStr">
+        <is>
+          <t>Design effect 2: intervals with the variance doubled (Wald F halved), a sensitivity value for the area-level clustering of the survey sample, which is not identified in the files; it is not a design-based variance estimate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="9" t="inlineStr">
+        <is>
+          <t>Matched households as clusters: households linked by member signature or reference-person key in any pair of survey years form one cluster (41,505 clusters for 76,693 household-years; 173 clusters contain two households of the same year). Re-interviews that could not be detected are treated as independent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="9" t="inlineStr">
+        <is>
+          <t>Income gradient: survey-weighted logistic regression on log relative income, restricted cubic spline with five knots at the 5th, 27.5th, 50th, 72.5th and 95th percentiles of pooled 2023–2025 log relative income (0.37, 0.69, 1.01, 1.51, 3.31 times the median), Harrell's default; the income-curve analysis was added after the written analysis plan. Two-curve tests pool the two years with year interactions; the three-year tests pool all years. Predictions and differences on the probability scale (delta method, full covariance matrix of the pooled model). Knot positions as quantiles of pooled log relative income; dAIC, design-based AIC (Lumley and Scott); largest difference over the 5th–95th weighted percentiles of relative income in each year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="9" t="inlineStr">
+        <is>
+          <t>Real value: the 60% line is 0.6 times the median equivalized disposable income of the income reference year (persons, FK050), deflated with the annual average consumer price index of the income year (2003 = 100: 2022, 967.71; 2023, 1,488.91; 2024, 2,360.03; 2025, 3,183.23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="9" t="inlineStr">
+        <is>
+          <t>Erreygers concentration index of meal-affordability deprivation by equivalized-income rank (persons, FK050); negative values indicate concentration among lower-income persons. –, not computed.</t>
         </is>
       </c>
     </row>
@@ -5102,7 +9797,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table S9. Univariable association of features with food insecurity (ten strongest per layer) and multivariable comparison of feature layers.</t>
+          <t>Table S9. Univariable association of features with meal-affordability deprivation (ten strongest per layer) and multivariable comparison of feature layers.</t>
         </is>
       </c>
     </row>
@@ -6810,7 +11505,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>LightGBM, + deprivation items (upper bound)</t>
+          <t>LightGBM, upper bound: + other deprivation items (same battery as the outcome)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -7622,7 +12317,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Food insecure, %</t>
+          <t>Meal-deprived, %</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -7632,7 +12327,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Food insecure, %</t>
+          <t>Meal-deprived, %</t>
         </is>
       </c>
       <c r="F4" s="12" t="n"/>
@@ -9480,7 +14175,7 @@
     <row r="92">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>Leaves are ordered by the training-year share food insecure; a rule set at a given targeting rate selects leaves in this order. Shares and prevalences weighted (HB040).</t>
+          <t>Leaves are ordered by the training-year share meal-deprived; a rule set at a given targeting rate selects leaves in this order. Shares and prevalences weighted (HB040).</t>
         </is>
       </c>
     </row>
@@ -11636,7 +16331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="48.71" customWidth="1" min="1" max="1"/>
@@ -11649,7 +16344,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 2. Food insecurity, income poverty and exclusion error of poverty-based identification, Turkey, 2023–2025.</t>
+          <t>Table 2. Meal-affordability deprivation, income poverty and exclusion error of poverty-based identification, Türkiye, 2023–2025.</t>
         </is>
       </c>
     </row>
@@ -11695,7 +16390,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Food insecurity</t>
+          <t>Meal-affordability deprivation</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -11715,7 +16410,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>−0.4 (−1.4, 0.6)</t>
+          <t>−0.4 (−1.3, 0.5)</t>
         </is>
       </c>
     </row>
@@ -11742,14 +16437,14 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>−0.3 (−1.0, 0.4)</t>
+          <t>−0.3 (−0.9, 0.3)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Food insecure and not poor</t>
+          <t>Meal-deprived and not poor</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -11769,14 +16464,14 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>−1.1 (−2.1, −0.2)</t>
+          <t>−1.1 (−2.0, −0.3)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Food insecurity among the poor (60% threshold)</t>
+          <t>Meal-affordability deprivation among the poor (60% threshold)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -11796,14 +16491,14 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>5.8 (3.7, 7.9)</t>
+          <t>5.8 (3.9, 7.8)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Households food insecure and not poor, millions</t>
+          <t>Meal-deprived, non-poor households, millions</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -11823,14 +16518,14 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>−0.19 (−0.45, 0.07)</t>
+          <t>−0.19 (−0.44, 0.07)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Exclusion error, % of food insecure not identified</t>
+          <t>Exclusion error, % of meal-deprived not identified</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr"/>
@@ -11861,7 +16556,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>−2.3 (−3.8, −0.8)</t>
+          <t>−2.3 (−3.7, −0.9)</t>
         </is>
       </c>
     </row>
@@ -11888,7 +16583,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>−0.9 (−2.2, 0.3)</t>
+          <t>−0.9 (−2.1, 0.2)</t>
         </is>
       </c>
     </row>
@@ -11915,7 +16610,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>−3.6 (−5.2, −1.9)</t>
+          <t>−3.6 (−5.0, −2.1)</t>
         </is>
       </c>
     </row>
@@ -11942,7 +16637,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>−0.9 (−2.6, 0.7)</t>
+          <t>−0.9 (−2.4, 0.6)</t>
         </is>
       </c>
     </row>
@@ -11969,7 +16664,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>−1.9 (−2.9, −0.8)</t>
+          <t>−1.9 (−2.8, −0.9)</t>
         </is>
       </c>
     </row>
@@ -11987,7 +16682,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Food insecurity</t>
+          <t>Meal-affordability deprivation</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -12007,7 +16702,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>−4.1 (−5.2, −2.9)</t>
+          <t>−4.1 (−5.1, −3.0)</t>
         </is>
       </c>
     </row>
@@ -12034,14 +16729,14 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>−0.6 (−1.7, 0.4)</t>
+          <t>−0.6 (−1.5, 0.3)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Food insecure and not poor</t>
+          <t>Meal-deprived and not poor</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -12061,14 +16756,14 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>−4.6 (−5.5, −3.6)</t>
+          <t>−4.6 (−5.5, −3.7)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Food insecurity among the poor (60% threshold)</t>
+          <t>Meal-affordability deprivation among the poor (60% threshold)</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -12088,14 +16783,14 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>4.5 (2.0, 7.0)</t>
+          <t>4.5 (2.1, 6.9)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Children (&lt;18 years) in food-insecure households, %</t>
+          <t>Children (&lt;18 years) living in meal-deprived households, %</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -12115,7 +16810,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>−4.6 (−6.4, −2.9)</t>
+          <t>−4.6 (−6.2, −3.1)</t>
         </is>
       </c>
     </row>
@@ -12142,14 +16837,14 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>−7.1 (−10.0, −4.3)</t>
+          <t>−7.1 (−9.7, −4.5)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Children in food-insecure, non-poor households, millions</t>
+          <t>Children living in meal-deprived, non-poor households, millions</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -12169,14 +16864,14 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>−1.28 (−1.62, −0.95)</t>
+          <t>−1.28 (−1.59, −0.98)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Exclusion error, % of food insecure not identified</t>
+          <t>Exclusion error, % of meal-deprived not identified</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr"/>
@@ -12207,7 +16902,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>−5.7 (−7.6, −3.7)</t>
+          <t>−5.7 (−7.5, −3.8)</t>
         </is>
       </c>
     </row>
@@ -12234,7 +16929,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>−3.7 (−5.5, −2.0)</t>
+          <t>−3.7 (−5.4, −2.1)</t>
         </is>
       </c>
     </row>
@@ -12261,7 +16956,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>−7.6 (−9.5, −5.6)</t>
+          <t>−7.6 (−9.4, −5.8)</t>
         </is>
       </c>
     </row>
@@ -12288,7 +16983,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>1.0 (−1.0, 2.9)</t>
+          <t>1.0 (−0.9, 2.8)</t>
         </is>
       </c>
     </row>
@@ -12315,14 +17010,14 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>−3.6 (−4.8, −2.4)</t>
+          <t>−3.6 (−4.7, −2.4)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Income gradient of food insecurity (households)</t>
+          <t>Income gradient of meal-affordability deprivation (households)</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr"/>
@@ -12333,22 +17028,22 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Non-linearity in log relative income</t>
+          <t>Association with log relative income, Wald F (4 df)</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>F = 23.6 (p &lt; 0.001)</t>
+          <t>F = 578.1 (p &lt; 0.001)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>F = 17.2 (p &lt; 0.001)</t>
+          <t>F = 623.5 (p &lt; 0.001)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>F = 48.4 (p &lt; 0.001)</t>
+          <t>F = 717.6 (p &lt; 0.001)</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -12356,22 +17051,22 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>Step at the 60% threshold, percentage points</t>
+          <t>Departure from linearity, Wald F (3 df)</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>5.8 (2.0, 9.6)</t>
+          <t>F = 23.6 (p &lt; 0.001)</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>4.3 (0.6, 8.0)</t>
+          <t>F = 17.2 (p &lt; 0.001)</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>4.8 (1.2, 8.4)</t>
+          <t>F = 48.4 (p &lt; 0.001)</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
@@ -12379,22 +17074,22 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>Step, seven-knot spline (sensitivity)</t>
+          <t>Step at the 60% threshold, percentage points</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>0.9 (−4.9, 6.6)</t>
+          <t>5.8 (2.0, 9.6)</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>1.0 (−4.5, 6.6)</t>
+          <t>4.3 (0.6, 8.0)</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.8 (−2.5, 8.2)</t>
+          <t>4.8 (1.2, 8.4)</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -12402,66 +17097,104 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
+          <t>Step, seven-knot spline (sensitivity)</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>0.9 (−4.9, 6.6)</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>1.0 (−4.5, 6.6)</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>2.8 (−2.5, 8.2)</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
           <t>Step, piecewise-linear (sensitivity)</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>0.7 (−2.4, 3.8)</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>0.8 (−2.2, 3.8)</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>−2.1 (−5.0, 0.8)</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>Change in the shape of the income curve</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr"/>
-      <c r="C35" s="5" t="inlineStr"/>
-      <c r="D35" s="5" t="inlineStr"/>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>F = 38.0 (p &lt; 0.001)</t>
-        </is>
-      </c>
+      <c r="E35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>Estimates are weighted percentages (95% CI) unless stated otherwise; 24,932, 25,925 and 25,836 households in 2023, 2024 and 2025. Food insecurity: household cannot afford a meal with meat, chicken or fish (or vegetarian equivalent) every second day (HE090). Exclusion error: share of food-insecure households (persons) not identified by the threshold.</t>
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Equality of the 2023 and 2025 curves, Wald F (5 df)</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr"/>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr"/>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>F = 33.5 (p &lt; 0.001)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>Taylor-linearization intervals with households as units; the area-level clustering of the survey sample is not identified in the files, so intervals are approximate (design-effect sensitivity in Supplementary Table S8). Differences assume independent samples. 2023 contains no households from TR63.</t>
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Equality of curve shape, 2023 and 2025, Wald F (4 df)</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr"/>
+      <c r="C37" s="5" t="inlineStr"/>
+      <c r="D37" s="5" t="inlineStr"/>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>F = 41.8 (p &lt; 0.001)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>MSD, material and social deprivation; 12 of the 13 Eurostat items (meat item excluded).</t>
+          <t>Estimates are weighted percentages (95% CI) unless stated otherwise; 24,932, 25,925 and 25,836 households in 2023, 2024 and 2025. Meal-affordability deprivation: household cannot afford a meal with meat, chicken or fish, or a vegetarian equivalent, every second day (HE090 = 2). Exclusion error: share of meal-deprived households (persons) not identified by the threshold.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>Income gradient: survey-weighted logistic regression of food insecurity on log relative income (restricted cubic spline, five knots). Non-linearity: Wald test of the three non-linear terms. Step: indicator for income below the 60% line added to the spline; difference in predicted probability at the line (sensitivity: seven knots, and a piecewise-linear model with a slope change and a jump at the line). Knots at quantiles of pooled 2023–2025 log relative income. Change in shape: Wald test of the year interaction with the slope and spline terms, 2023 and 2025 pooled; the test treats the two years as independent samples, although at least 42% of 2025 households were matched to a 2023 household, and ignores area clustering, so its p value is optimistic.</t>
+          <t>Taylor-linearization intervals; the area-level clustering of the survey sample is not identified in the files, so intervals are approximate (design-effect sensitivity in Supplementary Table S8). Year differences and year tests count households matched across survey years (in at least one pair of years) as one cluster; re-interviews that could not be detected are treated as independent. 2023 contains no households from TR63.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>MSD, material and social deprivation; 12 of the 13 Eurostat items (meat item excluded).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>Income gradient: survey-weighted logistic regression of meal-affordability deprivation on log relative income (restricted cubic spline, five knots at the 5th, 27.5th, 50th, 72.5th and 95th percentiles of pooled 2023–2025 log relative income, i.e., 0.37, 0.69, 1.01, 1.51, 3.31 times the median). Association: Wald test that all four income terms are zero. Departure from linearity: Wald test of the three non-linear terms. Step: indicator for income below the 60% line added to the spline; difference in predicted probability at the line (sensitivity: seven knots, and a piecewise-linear model with a slope change and a jump at the line). Equality of curves: Wald test of the year term and its interactions with the four income terms, 2023 and 2025 pooled; equality of shape: the four interactions only.</t>
         </is>
       </c>
     </row>
@@ -12477,7 +17210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="48.71" customWidth="1" min="1" max="1"/>
@@ -13287,7 +18020,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>LightGBM, + deprivation items (upper bound)</t>
+          <t>LightGBM, upper bound: + other deprivation items (same battery as the outcome)</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -13715,70 +18448,937 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>LightGBM, + financial strain</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>47.7</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>9.5 (7.6, 11.5)</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>47.1</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>9.4 (7.3, 11.5)</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>46.9</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>11.1 (9.5, 12.5)</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>50.9</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>12.6 (11.4, 13.8)</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr"/>
-      <c r="K27" s="5" t="inlineStr"/>
-      <c r="L27" s="5" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr"/>
+      <c r="L27" s="4" t="inlineStr">
         <is>
           <t>0.870</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>All households, main test set calibrated to the 2025 household population: sensitivity at the poverty line's targeting rate (16.0%; n = 7,861)</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr"/>
+      <c r="C28" s="4" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr"/>
+      <c r="I28" s="4" t="inlineStr"/>
+      <c r="J28" s="4" t="inlineStr"/>
+      <c r="K28" s="4" t="inlineStr"/>
+      <c r="L28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Poverty line (60% of median income)</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>31.5</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr"/>
+      <c r="D29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr"/>
+      <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" s="4" t="inlineStr"/>
+      <c r="J29" s="4" t="inlineStr"/>
+      <c r="K29" s="4" t="inlineStr"/>
+      <c r="L29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Ranking by relative income</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>31.5</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr"/>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" s="4" t="inlineStr"/>
+      <c r="J30" s="4" t="inlineStr"/>
+      <c r="K30" s="4" t="inlineStr"/>
+      <c r="L30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Rule set (depth-3 tree), structural</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>29.8</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>−1.8 (−3.3, −0.2)</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" s="4" t="inlineStr"/>
+      <c r="J31" s="4" t="inlineStr"/>
+      <c r="K31" s="4" t="inlineStr"/>
+      <c r="L31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Rule set (depth-3 tree), register-like</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>−1.5 (−2.7, −0.3)</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr"/>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr"/>
+      <c r="H32" s="4" t="inlineStr"/>
+      <c r="I32" s="4" t="inlineStr"/>
+      <c r="J32" s="4" t="inlineStr"/>
+      <c r="K32" s="4" t="inlineStr"/>
+      <c r="L32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Rule set (depth-3 tree), income + structural</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>31.5</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>−0.1 (−0.4, 0.2)</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="4" t="inlineStr"/>
+      <c r="J33" s="4" t="inlineStr"/>
+      <c r="K33" s="4" t="inlineStr"/>
+      <c r="L33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Lasso logistic (≤6 variables), structural</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>31.8</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>0.3 (−1.0, 1.7)</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr"/>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr"/>
+      <c r="H34" s="4" t="inlineStr"/>
+      <c r="I34" s="4" t="inlineStr"/>
+      <c r="J34" s="4" t="inlineStr"/>
+      <c r="K34" s="4" t="inlineStr"/>
+      <c r="L34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Lasso logistic (≤6 variables), income + structural</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>35.3</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>3.7 (2.8, 4.8)</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" s="4" t="inlineStr"/>
+      <c r="J35" s="4" t="inlineStr"/>
+      <c r="K35" s="4" t="inlineStr"/>
+      <c r="L35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Ridge logistic (linear), income + structural</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>35.5</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>3.9 (2.8, 5.1)</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr"/>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr"/>
+      <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" s="4" t="inlineStr"/>
+      <c r="J36" s="4" t="inlineStr"/>
+      <c r="K36" s="4" t="inlineStr"/>
+      <c r="L36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Ridge logistic (splines), income + structural</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>34.8</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>3.3 (2.2, 4.6)</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr"/>
+      <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" s="4" t="inlineStr"/>
+      <c r="J37" s="4" t="inlineStr"/>
+      <c r="K37" s="4" t="inlineStr"/>
+      <c r="L37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>LightGBM, register-like subset</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>32.3</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>0.8 (−0.5, 2.1)</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr"/>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="4" t="inlineStr"/>
+      <c r="J38" s="4" t="inlineStr"/>
+      <c r="K38" s="4" t="inlineStr"/>
+      <c r="L38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>LightGBM, structural only</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>32.9</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>1.4 (0.2, 2.7)</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr"/>
+      <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr"/>
+      <c r="J39" s="4" t="inlineStr"/>
+      <c r="K39" s="4" t="inlineStr"/>
+      <c r="L39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>LightGBM, income + structural</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>35.2</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>3.7 (2.5, 4.8)</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr"/>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="4" t="inlineStr"/>
+      <c r="J40" s="4" t="inlineStr"/>
+      <c r="K40" s="4" t="inlineStr"/>
+      <c r="L40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>LightGBM, + financial strain</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>36.3</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>4.8 (3.7, 6.0)</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr"/>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr"/>
+      <c r="G41" s="4" t="inlineStr"/>
+      <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr"/>
+      <c r="J41" s="4" t="inlineStr"/>
+      <c r="K41" s="4" t="inlineStr"/>
+      <c r="L41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>LightGBM, upper bound: + other deprivation items (same battery as the outcome)</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>9.5 (8.3, 10.7)</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr"/>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr"/>
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="4" t="inlineStr"/>
+      <c r="J42" s="4" t="inlineStr"/>
+      <c r="K42" s="4" t="inlineStr"/>
+      <c r="L42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>Multilayer perceptron, income + structural</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>34.8</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>3.3 (2.1, 4.5)</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr"/>
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr"/>
+      <c r="G43" s="4" t="inlineStr"/>
+      <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" s="4" t="inlineStr"/>
+      <c r="J43" s="4" t="inlineStr"/>
+      <c r="K43" s="4" t="inlineStr"/>
+      <c r="L43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Multilayer perceptron, structural only</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>33.5</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>1.9 (0.8, 3.3)</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr"/>
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr"/>
+      <c r="G44" s="4" t="inlineStr"/>
+      <c r="H44" s="4" t="inlineStr"/>
+      <c r="I44" s="4" t="inlineStr"/>
+      <c r="J44" s="4" t="inlineStr"/>
+      <c r="K44" s="4" t="inlineStr"/>
+      <c r="L44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>All households, main test set excluding TR63: sensitivity at the poverty line's targeting rate (14.7%; n = 7,566)</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr"/>
+      <c r="C45" s="4" t="inlineStr"/>
+      <c r="D45" s="4" t="inlineStr"/>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr"/>
+      <c r="G45" s="4" t="inlineStr"/>
+      <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" s="4" t="inlineStr"/>
+      <c r="J45" s="4" t="inlineStr"/>
+      <c r="K45" s="4" t="inlineStr"/>
+      <c r="L45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>Poverty line (60% of median income)</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>29.0</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr"/>
+      <c r="D46" s="4" t="inlineStr"/>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr"/>
+      <c r="G46" s="4" t="inlineStr"/>
+      <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" s="4" t="inlineStr"/>
+      <c r="J46" s="4" t="inlineStr"/>
+      <c r="K46" s="4" t="inlineStr"/>
+      <c r="L46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>Ranking by relative income</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>29.0</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr"/>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr"/>
+      <c r="G47" s="4" t="inlineStr"/>
+      <c r="H47" s="4" t="inlineStr"/>
+      <c r="I47" s="4" t="inlineStr"/>
+      <c r="J47" s="4" t="inlineStr"/>
+      <c r="K47" s="4" t="inlineStr"/>
+      <c r="L47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>Rule set (depth-3 tree), structural</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>28.1</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>−0.9 (−2.5, 0.6)</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr"/>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
+      <c r="G48" s="4" t="inlineStr"/>
+      <c r="H48" s="4" t="inlineStr"/>
+      <c r="I48" s="4" t="inlineStr"/>
+      <c r="J48" s="4" t="inlineStr"/>
+      <c r="K48" s="4" t="inlineStr"/>
+      <c r="L48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Rule set (depth-3 tree), register-like</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>27.3</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>−1.7 (−2.8, −0.5)</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr"/>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr"/>
+      <c r="G49" s="4" t="inlineStr"/>
+      <c r="H49" s="4" t="inlineStr"/>
+      <c r="I49" s="4" t="inlineStr"/>
+      <c r="J49" s="4" t="inlineStr"/>
+      <c r="K49" s="4" t="inlineStr"/>
+      <c r="L49" s="4" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>Rule set (depth-3 tree), income + structural</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>29.0</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>0.0 (−0.3, 0.3)</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr"/>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
+      <c r="G50" s="4" t="inlineStr"/>
+      <c r="H50" s="4" t="inlineStr"/>
+      <c r="I50" s="4" t="inlineStr"/>
+      <c r="J50" s="4" t="inlineStr"/>
+      <c r="K50" s="4" t="inlineStr"/>
+      <c r="L50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>Lasso logistic (≤6 variables), structural</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>29.7</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>0.7 (−0.8, 2.0)</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr"/>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
+      <c r="G51" s="4" t="inlineStr"/>
+      <c r="H51" s="4" t="inlineStr"/>
+      <c r="I51" s="4" t="inlineStr"/>
+      <c r="J51" s="4" t="inlineStr"/>
+      <c r="K51" s="4" t="inlineStr"/>
+      <c r="L51" s="4" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>Lasso logistic (≤6 variables), income + structural</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>32.2</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>3.3 (2.3, 4.2)</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr"/>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr"/>
+      <c r="G52" s="4" t="inlineStr"/>
+      <c r="H52" s="4" t="inlineStr"/>
+      <c r="I52" s="4" t="inlineStr"/>
+      <c r="J52" s="4" t="inlineStr"/>
+      <c r="K52" s="4" t="inlineStr"/>
+      <c r="L52" s="4" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>Ridge logistic (linear), income + structural</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>32.7</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>3.7 (2.7, 4.8)</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr"/>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
+      <c r="G53" s="4" t="inlineStr"/>
+      <c r="H53" s="4" t="inlineStr"/>
+      <c r="I53" s="4" t="inlineStr"/>
+      <c r="J53" s="4" t="inlineStr"/>
+      <c r="K53" s="4" t="inlineStr"/>
+      <c r="L53" s="4" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>Ridge logistic (splines), income + structural</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>32.4</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>3.4 (2.4, 4.5)</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr"/>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr"/>
+      <c r="G54" s="4" t="inlineStr"/>
+      <c r="H54" s="4" t="inlineStr"/>
+      <c r="I54" s="4" t="inlineStr"/>
+      <c r="J54" s="4" t="inlineStr"/>
+      <c r="K54" s="4" t="inlineStr"/>
+      <c r="L54" s="4" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>LightGBM, register-like subset</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>29.4</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>0.4 (−0.8, 1.7)</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr"/>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
+      <c r="G55" s="4" t="inlineStr"/>
+      <c r="H55" s="4" t="inlineStr"/>
+      <c r="I55" s="4" t="inlineStr"/>
+      <c r="J55" s="4" t="inlineStr"/>
+      <c r="K55" s="4" t="inlineStr"/>
+      <c r="L55" s="4" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>LightGBM, structural only</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>30.8</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>1.8 (0.6, 3.0)</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr"/>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
+      <c r="G56" s="4" t="inlineStr"/>
+      <c r="H56" s="4" t="inlineStr"/>
+      <c r="I56" s="4" t="inlineStr"/>
+      <c r="J56" s="4" t="inlineStr"/>
+      <c r="K56" s="4" t="inlineStr"/>
+      <c r="L56" s="4" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>LightGBM, income + structural</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>32.5</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>3.6 (2.5, 4.6)</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr"/>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr"/>
+      <c r="G57" s="4" t="inlineStr"/>
+      <c r="H57" s="4" t="inlineStr"/>
+      <c r="I57" s="4" t="inlineStr"/>
+      <c r="J57" s="4" t="inlineStr"/>
+      <c r="K57" s="4" t="inlineStr"/>
+      <c r="L57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>LightGBM, + financial strain</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>33.4</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>4.5 (3.4, 5.6)</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr"/>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr"/>
+      <c r="H58" s="4" t="inlineStr"/>
+      <c r="I58" s="4" t="inlineStr"/>
+      <c r="J58" s="4" t="inlineStr"/>
+      <c r="K58" s="4" t="inlineStr"/>
+      <c r="L58" s="4" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>LightGBM, upper bound: + other deprivation items (same battery as the outcome)</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>37.4</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>8.4 (7.3, 9.6)</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr"/>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
+      <c r="G59" s="4" t="inlineStr"/>
+      <c r="H59" s="4" t="inlineStr"/>
+      <c r="I59" s="4" t="inlineStr"/>
+      <c r="J59" s="4" t="inlineStr"/>
+      <c r="K59" s="4" t="inlineStr"/>
+      <c r="L59" s="4" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>Multilayer perceptron, income + structural</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>32.2</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>3.3 (2.2, 4.4)</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr"/>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
+      <c r="G60" s="4" t="inlineStr"/>
+      <c r="H60" s="4" t="inlineStr"/>
+      <c r="I60" s="4" t="inlineStr"/>
+      <c r="J60" s="4" t="inlineStr"/>
+      <c r="K60" s="4" t="inlineStr"/>
+      <c r="L60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>Multilayer perceptron, structural only</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>31.0</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>2.0 (0.8, 3.2)</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr"/>
+      <c r="E61" s="5" t="inlineStr"/>
+      <c r="F61" s="5" t="inlineStr"/>
+      <c r="G61" s="5" t="inlineStr"/>
+      <c r="H61" s="5" t="inlineStr"/>
+      <c r="I61" s="5" t="inlineStr"/>
+      <c r="J61" s="5" t="inlineStr"/>
+      <c r="K61" s="5" t="inlineStr"/>
+      <c r="L61" s="5" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
         <is>
           <t>Main test set: 2025 households not matched to 2023 or 2024 by member signature or reference-person key. Strict cleaning: additionally excludes households whose reference-person key or member signature occurs in 2023 or 2024 at all, including keys shared by several households. Signature-only cleaning: households unmatched by member signature alone (keeps re-interviewed one-person households and households whose composition changed). Full 2025 sample: all households. Trained on 2023 only: models trained on 2023 and tested on 2025 households not matched to 2023; hyperparameters were taken from the main tuning, whose folds include a 2024 training fold (no 2025 data were used).</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
         <is>
           <t>Δ: paired bootstrap difference in sensitivity from the poverty line at its targeting rate (all households) or from income ranking at the same targeting rate (non-poor households), in the same test set; 95% CI from 8,000 household bootstrap replicates. –, identical to the poverty line by construction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>Last two blocks (values in the main-test-set columns): calibrated, HB040 weights of the main test set raked to the weighted 2025 household totals of household type, household size (1–5, ≥6), NUTS 1 region, age group of the reference person, tenure (owner; tenant; employer-provided or rent-free) and relative income band, with weight ratios bounded to [0.2, 5] (observed 0.50–1.66); raking repeated in every bootstrap replicate; the performance estimates refer to the 2025 household population rather than to households not matched to an earlier survey. Excluding TR63: the 295 main-test-set households of TR63 removed, original weights, targeting rate equal to the poverty rate of this subset (the 2023 training data contain no TR63 households).</t>
         </is>
       </c>
     </row>
@@ -13802,6 +19402,519 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col width="48.71" customWidth="1" min="1" max="1"/>
+    <col width="16.71" customWidth="1" min="2" max="2"/>
+    <col width="16.71" customWidth="1" min="3" max="3"/>
+    <col width="16.71" customWidth="1" min="4" max="4"/>
+    <col width="16.71" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Table S–. Additional meal-deprived households and children reached at the poverty line's caseload, 2025 population (thousands).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Meal-deprived households</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Children living in meal-deprived households</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Δ sensitivity, pp</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Additional households reached, thousands</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Δ children, pp</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Additional children reached, thousands</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Sparse rules, structural</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr"/>
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Rule set (depth-3 tree), structural</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>−1.8 (−3.3, −0.2)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>−177 (−328, −19)</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>−25.3 (−29.6, −20.8)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>−2,145 (−2,508, −1,767)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Rule set (depth-3 tree), register-like</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>−1.5 (−2.7, −0.3)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>−154 (−274, −30)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>−26.8 (−30.6, −22.9)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>−2,274 (−2,593, −1,945)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Lasso logistic (≤6 variables), structural</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>0.3 (−1.0, 1.7)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>25 (−103, 175)</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>−24.6 (−28.9, −20.2)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>−2,082 (−2,447, −1,712)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Sparse rules, income + structural</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Rule set (depth-3 tree), income + structural</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>−0.1 (−0.4, 0.2)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>−7 (−38, 22)</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>−0.2 (−1.1, 0.8)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>−17 (−95, 69)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Lasso logistic (≤6 variables), income + structural</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>3.7 (2.8, 4.8)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>375 (278, 486)</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>−2.8 (−5.9, 0.4)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>−233 (−497, 34)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Prediction models</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr"/>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Ridge logistic (linear), income + structural</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>3.9 (2.8, 5.1)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>397 (283, 508)</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>−8.8 (−12.4, −5.0)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>−742 (−1,049, −424)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Ridge logistic (splines), income + structural</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>3.3 (2.2, 4.6)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>331 (224, 461)</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>−9.9 (−13.7, −5.9)</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>−835 (−1,164, −503)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>LightGBM, register-like subset</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>0.8 (−0.5, 2.1)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>79 (−51, 210)</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>−10.9 (−14.9, −6.9)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>−921 (−1,260, −587)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>LightGBM, structural only</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>1.4 (0.2, 2.7)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>141 (17, 275)</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>−14.4 (−18.3, −10.0)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>−1,219 (−1,551, −845)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>LightGBM, income + structural</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>3.7 (2.5, 4.8)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>369 (251, 485)</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>−8.8 (−12.6, −5.3)</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>−744 (−1,068, −450)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>LightGBM, + financial strain</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>4.8 (3.7, 6.0)</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>480 (367, 607)</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>−10.4 (−14.4, −6.4)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>−882 (−1,222, −540)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Multilayer perceptron, income + structural</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>3.3 (2.1, 4.5)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>327 (213, 452)</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>−10.7 (−14.3, −6.8)</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>−903 (−1,211, −575)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Multilayer perceptron, structural only</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>1.9 (0.8, 3.3)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>195 (77, 336)</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>−13.9 (−17.9, −9.7)</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>−1,178 (−1,521, −825)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Upper bound</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr"/>
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>LightGBM, upper bound: + other deprivation items (same battery as the outcome)</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>9.5 (8.3, 10.7)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>953 (832, 1,079)</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>−23.7 (−27.7, −20.3)</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>−2,010 (−2,350, −1,717)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>Differences from the poverty line at its targeting rate in the main test set calibrated to the 2025 household population (95% CI, paired household bootstrap, 8,000 replicates with raking repeated in each), multiplied by the weighted number of meal-deprived households in 2025 (10.05 million, HB040) or of children living in them (8.48 million, FK050): households (children) reached when the same number of households is selected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>Scale: the poverty line selects 4.35 million households and misses 6.84 million meal-deprived households in 2025; its calibrated sensitivity is 31.5% and it reaches 61.9% of the children living in meal-deprived households. The population totals are treated as fixed. Upper bound: model with the other deprivation items of the same battery as the outcome.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="D3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
@@ -13817,7 +19930,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table S16. Standardized prevalence of low dietary frequency and heavy health-cost burden among food-insecure, non-poor adults and households, by model specification, 2025.</t>
+          <t>Table S16. Standardized prevalence of low consumption frequency and heavy health-cost burden among meal-deprived, non-poor adults and households, by model specification, 2025.</t>
         </is>
       </c>
     </row>
@@ -14642,7 +20755,7 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>C2: G2 vs G3 (food insecure) · Meat &lt;1/week</t>
+          <t>C2: G2 vs G3 (meal-deprived) · Meat &lt;1/week</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr"/>
@@ -14902,7 +21015,7 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>C2: G2 vs G3 (food insecure) · Fruit &lt;1/day</t>
+          <t>C2: G2 vs G3 (meal-deprived) · Fruit &lt;1/day</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr"/>
@@ -15162,7 +21275,7 @@
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>C2: G2 vs G3 (food insecure) · Vegetables &lt;1/day</t>
+          <t>C2: G2 vs G3 (meal-deprived) · Vegetables &lt;1/day</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr"/>
@@ -15682,7 +21795,7 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>C2: G2 vs G3 (food insecure) · Health costs heavy burden</t>
+          <t>C2: G2 vs G3 (meal-deprived) · Health costs heavy burden</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr"/>
@@ -15942,7 +22055,7 @@
     <row r="68">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>Reference: G1 (food secure, not poor) in C1 and G3 (food insecure and poor) in C2. Standardized by g-computation to the comparison population; weights FB030 (adults) or HB040 (households). Crude: weighted prevalences in the same analytic sample without adjustment or standardization.</t>
+          <t>Reference: G1 (not meal-deprived, not poor) in C1 and G3 (meal-deprived and poor) in C2. Standardized by g-computation to the comparison population; weights FB030 (adults) or HB040 (households). Crude: weighted prevalences in the same analytic sample without adjustment or standardization.</t>
         </is>
       </c>
     </row>
@@ -15959,7 +22072,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15977,7 +22090,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table S–. Analytic samples of the dietary and health-cost comparisons: numbers, events and crude weighted prevalences by group, 2025.</t>
+          <t>Table S–. Analytic samples of the consumption-frequency and health-cost comparisons: numbers, events and crude weighted prevalences by group, 2025.</t>
         </is>
       </c>
     </row>
@@ -16017,7 +22130,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>G1 food secure, all</t>
+          <t>G1 not meal-deprived, all</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -16039,7 +22152,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>G1 food secure, not poor (reference in C1)</t>
+          <t>G1 not meal-deprived, not poor (reference in C1)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -16061,7 +22174,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>G2 food insecure, not poor</t>
+          <t>G2 meal-deprived, not poor</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -16083,7 +22196,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>G3 food insecure and poor (reference in C2)</t>
+          <t>G3 meal-deprived and poor (reference in C2)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -16115,7 +22228,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>G1 food secure, all</t>
+          <t>G1 not meal-deprived, all</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -16137,7 +22250,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>G1 food secure, not poor (reference in C1)</t>
+          <t>G1 not meal-deprived, not poor (reference in C1)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -16159,7 +22272,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>G2 food insecure, not poor</t>
+          <t>G2 meal-deprived, not poor</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -16181,7 +22294,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>G3 food insecure and poor (reference in C2)</t>
+          <t>G3 meal-deprived and poor (reference in C2)</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -16213,7 +22326,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>G1 food secure, all</t>
+          <t>G1 not meal-deprived, all</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -16235,7 +22348,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>G1 food secure, not poor (reference in C1)</t>
+          <t>G1 not meal-deprived, not poor (reference in C1)</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -16257,7 +22370,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>G2 food insecure, not poor</t>
+          <t>G2 meal-deprived, not poor</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -16279,7 +22392,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>G3 food insecure and poor (reference in C2)</t>
+          <t>G3 meal-deprived and poor (reference in C2)</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -16311,7 +22424,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>G1 food secure, all</t>
+          <t>G1 not meal-deprived, all</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -16333,7 +22446,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>G1 food secure, not poor (reference in C1)</t>
+          <t>G1 not meal-deprived, not poor (reference in C1)</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -16355,7 +22468,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>G2 food insecure, not poor</t>
+          <t>G2 meal-deprived, not poor</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -16377,7 +22490,7 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>G3 food insecure and poor (reference in C2)</t>
+          <t>G3 meal-deprived and poor (reference in C2)</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -16406,7 +22519,7 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>C1 compares G2 with food-secure adults who are not poor, so its reference is not all of G1. Crude differences and prevalence ratios are the first row of each block in Supplementary Table S16.</t>
+          <t>C1 compares G2 with adults who are neither meal-deprived nor poor, so its reference is not all of G1. Crude differences and prevalence ratios are the first row of each block in Supplementary Table S16.</t>
         </is>
       </c>
     </row>
@@ -16416,7 +22529,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16435,7 +22548,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table S17. Additional dietary and health-cost estimates: three-group standardization, income gradient among the food insecure, and sensitivity analyses, 2025.</t>
+          <t>Table S17. Additional consumption-frequency and health-cost estimates: three-group standardization, income gradient among the meal-deprived, and sensitivity analyses, 2025.</t>
         </is>
       </c>
     </row>
@@ -16481,7 +22594,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>G1 food secure, %</t>
+          <t>G1 not meal-deprived, %</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -16508,7 +22621,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>G2 food insecure, not poor, %</t>
+          <t>G2 meal-deprived, not poor, %</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -16535,7 +22648,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>G3 food insecure and poor, %</t>
+          <t>G3 meal-deprived and poor, %</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -16670,7 +22783,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Food-insecure adults (households) by equivalized income relative to the median, %</t>
+          <t>Meal-deprived adults (households) by equivalized income relative to the median, %</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr"/>
@@ -16843,7 +22956,7 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Meat &lt;1/week with vegetarian or vegan adults counted as low intake</t>
+          <t>Meat &lt;1/week with vegetarian or vegan adults counted as low frequency</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr"/>
@@ -16901,7 +23014,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17480,7 +23593,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17503,7 +23616,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table S19. Simulation S2: exclusion error and targeting performance under misclassification of the food insecurity item, by design of the misclassification.</t>
+          <t>Table S19. Simulation S2: exclusion error and targeting performance under misclassification of the meal item, by design of the misclassification.</t>
         </is>
       </c>
     </row>
@@ -19565,14 +25678,14 @@
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>Exclusion error: share of food-insecure households (persons) that are not income poor, implied by sensitivity (Se), specificity (Sp) and the observed prevalences in cells of equivalized income quintile × poverty status (closed form; the same under both designs). Differences: sensitivity at the poverty line's targeting rate minus that of the poverty line in the 2025 main test set, mean of 200 simulated assignments of true status; rule set, depth-3 tree on structural features; LightGBM, income + structural features; observed −0.9 and 3.6 pp.</t>
+          <t>Exclusion error: share of meal-deprived households (persons) that are not income poor, implied by sensitivity (Se), specificity (Sp) and the observed prevalences in cells of equivalized income quintile × poverty status (closed form; the same under both designs). Differences: sensitivity at the poverty line's targeting rate minus that of the poverty line in the 2025 main test set, mean of 200 simulated assignments of true status; rule set, depth-3 tree on structural features; LightGBM, income + structural features; observed −0.9 and 3.6 pp.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>Design A: Se and Sp hold within each cell, and true status is assigned by Bayes' rule from the cell's observed prevalence, so within a cell it depends on household characteristics only through the observed item. Design B: Se and Sp hold for every household, and true status is assigned from each household's calibrated probability of reporting food insecurity (out-of-time LightGBM score recalibrated on 2025 households with cell indicators and a restricted cubic spline of its logit).</t>
+          <t>Design A: Se and Sp hold within each cell, and true status is assigned by Bayes' rule from the cell's observed prevalence, so within a cell it depends on household characteristics only through the observed item. Design B: Se and Sp hold for every household, and true status is assigned from each household's calibrated probability of reporting meal-affordability deprivation (out-of-time LightGBM score recalibrated on 2025 households with cell indicators and a restricted cubic spline of its logit).</t>
         </is>
       </c>
     </row>
@@ -19625,7 +25738,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19782,6 +25895,1145 @@
       <c r="A7" s="9" t="inlineStr">
         <is>
           <t>95% percentile intervals from 200 household bootstrap replicates (Rao–Wu–Yue rescaled bootstrap) per simulated sample; MCSE, Monte Carlo standard error. SE, standard error. True value: the value in the pseudo-population, whose outcomes are model-based, so it differs from the observed exclusion error (68.1%).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col width="48.71" customWidth="1" min="1" max="1"/>
+    <col width="16.71" customWidth="1" min="2" max="2"/>
+    <col width="16.71" customWidth="1" min="3" max="3"/>
+    <col width="16.71" customWidth="1" min="4" max="4"/>
+    <col width="16.71" customWidth="1" min="5" max="5"/>
+    <col width="16.71" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Table S–. Design effect at which the 95% confidence interval of each principal contrast would include zero, and intervals under design effects of 2 and 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Contrast</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Estimate (95% CI)</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Design effect at which the 95% CI includes zero</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>95% CI, design effect 2</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>95% CI, design effect 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>H1: differences between 2025 and 2023, households matched across survey years as clusters</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Exclusion error of the 60% line, households, pp</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>−2.3 (−3.7, −0.9)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>−2.3 (−4.2, −0.4)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>−2.3 (−4.7, 0.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Exclusion error of the 60% line, persons, pp</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>−5.7 (−7.5, −3.8)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>9.7</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>−5.7 (−8.2, −3.1)</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>−5.7 (−8.8, −2.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Prevalence of meal-affordability deprivation, persons, pp</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>−4.1 (−5.1, −3.0)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>15.3</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>−4.1 (−5.5, −2.6)</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>−4.1 (−5.9, −2.3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Income curve at 0.6 times the median, pp</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>5.1 (3.1, 7.1)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>5.1 (2.3, 7.9)</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>5.1 (1.7, 8.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Income curve at 2.0 times the median, pp</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>−7.3 (−8.7, −5.9)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>27.2</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>−7.3 (−9.2, −5.3)</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>−7.3 (−9.7, −4.9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Erreygers concentration index</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>−0.092 (−0.112, −0.072)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>0.0101</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>21.8</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>−0.092 (−0.120, −0.064)</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>−0.092 (−0.126, −0.058)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>H2: paired differences at the poverty line's targeting rate, 2025 main test set (bootstrap SE)</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Δ sensitivity from the poverty line, Rule set (depth-3 tree), structural, pp</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>−0.9 (−2.5, 0.7)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>0.81</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.34</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="9"/>
+              <vertAlign val="superscript"/>
+            </rPr>
+            <t>a</t>
+          </r>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>−0.9 (−3.2, 1.3)</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>−0.9 (−3.7, 1.8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Δ sensitivity from the poverty line, Rule set (depth-3 tree), register-like, pp</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>−1.3 (−2.4, −0.2)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>−1.3 (−2.9, 0.3)</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>−1.3 (−3.3, 0.7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Δ sensitivity from the poverty line, Lasso logistic (≤6 variables), structural, pp</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>0.8 (−0.6, 2.2)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.33</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="9"/>
+              <vertAlign val="superscript"/>
+            </rPr>
+            <t>a</t>
+          </r>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>0.8 (−1.2, 2.8)</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>0.8 (−1.6, 3.2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Δ sensitivity from the poverty line, Rule set (depth-3 tree), income + structural, pp</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>0.0 (−0.3, 0.3)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="9"/>
+              <vertAlign val="superscript"/>
+            </rPr>
+            <t>a</t>
+          </r>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>0.0 (−0.4, 0.4)</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>0.0 (−0.5, 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Δ sensitivity from the poverty line, Lasso logistic (≤6 variables), income + structural, pp</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>3.6 (2.6, 4.5)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>13.7</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>3.6 (2.2, 5.0)</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>3.6 (1.9, 5.3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Δ sensitivity from the poverty line, Ridge logistic (linear), income + structural, pp</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>3.9 (2.9, 5.0)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>3.9 (2.4, 5.3)</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>3.9 (2.1, 5.6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Δ sensitivity from the poverty line, Ridge logistic (splines), income + structural, pp</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>3.6 (2.4, 4.6)</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>10.6</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>3.6 (2.0, 5.1)</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>3.6 (1.7, 5.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Δ sensitivity from the poverty line, LightGBM, register-like subset, pp</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>1.0 (−0.3, 2.1)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.64</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="9"/>
+              <vertAlign val="superscript"/>
+            </rPr>
+            <t>a</t>
+          </r>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>1.0 (−0.8, 2.7)</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>1.0 (−1.1, 3.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Δ sensitivity from the poverty line, LightGBM, structural only, pp</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>1.7 (0.6, 3.0)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>1.7 (0.0, 3.4)</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>1.7 (−0.4, 3.8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Δ sensitivity from the poverty line, LightGBM, income + structural, pp</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>3.6 (2.6, 4.7)</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>3.6 (2.1, 5.2)</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>3.6 (1.8, 5.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Δ sensitivity from the poverty line, LightGBM, + financial strain, pp</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>4.9 (3.8, 6.0)</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>19.7</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>4.9 (3.3, 6.5)</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>4.9 (3.0, 6.8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Children: lasso − LightGBM, income + structural, pp</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>6.4 (3.2, 9.1)</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>6.4 (2.2, 10.5)</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>6.4 (1.3, 11.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Marginal contribution of income, LightGBM (income + structural − structural only), pp</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>1.9 (1.0, 2.7)</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>1.9 (0.7, 3.1)</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>1.9 (0.5, 3.4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Marginal contribution of income, ridge logistic (linear), pp</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>1.6 (0.9, 2.5)</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>1.6 (0.5, 2.8)</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>1.6 (0.3, 3.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>H3: standardized differences, 2025 (bootstrap SE)</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr"/>
+      <c r="C26" s="4" t="inlineStr"/>
+      <c r="D26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>C1: G2 vs G1 (non-poor), Meat &lt;1/week, pp</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>25.5 (22.5, 29.6)</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>53.1</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>25.5 (20.5, 30.4)</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>25.5 (19.4, 31.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>C1: G2 vs G1 (non-poor), Fruit &lt;1/day, pp</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>14.2 (11.1, 17.0)</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>22.8</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>14.2 (10.0, 18.4)</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>14.2 (9.0, 19.3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>C1: G2 vs G1 (non-poor), Vegetables &lt;1/day, pp</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>13.0 (9.7, 16.7)</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>13.8</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>13.0 (8.1, 18.0)</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>13.0 (6.9, 19.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>C1: G2 vs G1 (non-poor), Health costs heavy burden, pp</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>5.8 (4.5, 7.1)</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>19.7</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>5.8 (4.0, 7.7)</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>5.8 (3.5, 8.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>C2: G2 vs G3 (meal-deprived), Meat &lt;1/week, pp</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>−6.2 (−9.3, −3.1)</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>−6.2 (−10.6, −1.8)</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>−6.2 (−11.6, −0.8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Three groups standardized to all adults (households): G2 − G3, Meat &lt;1/week, pp</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>−4.3 (−7.4, −1.4)</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>−4.3 (−8.5, −0.1)</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>−4.3 (−9.4, 0.8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Three groups standardized to all adults (households): G2 − G3, Fruit &lt;1/day, pp</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>−3.0 (−5.3, −0.7)</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>−3.0 (−6.3, 0.3)</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>−3.0 (−7.0, 1.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Three groups standardized to all adults (households): G2 − G3, Vegetables &lt;1/day, pp</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>−4.2 (−6.9, −1.4)</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>−4.2 (−8.1, −0.3)</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>−4.2 (−8.9, 0.6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Three groups standardized to all adults (households): G2 − G3, Health costs heavy burden, pp</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>−2.9 (−4.7, −1.1)</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>−2.9 (−5.5, −0.3)</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>−2.9 (−6.1, 0.3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="8"/>
+            </rPr>
+            <t>The released files contain no stratum, primary-sampling-unit, rotation-group or replicate-weight variables, so the design effect of the area-level clustering cannot be estimated. Design effect at which the interval includes zero: k* = (|estimate| / (1.96 × SE))</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="8"/>
+              <vertAlign val="superscript"/>
+            </rPr>
+            <t>2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="8"/>
+            </rPr>
+            <t>; an interval computed with the variance multiplied by k* just reaches zero. Intervals under design effects of 2 and 3: estimate ± 1.96 × SE × √k. These are sensitivity values, not design-based variance estimates.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">SE: linearization (H1, households matched across survey years as clusters) or standard deviation of the household bootstrap replicates (H2, 8,000 replicates; H3, 4,000 replicates for the main models and 2,000 for the three-group standardization); the 95% CI in the second column is the main-analysis interval (percentile interval for bootstrap estimates). </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="8"/>
+              <vertAlign val="superscript"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve"> The 95% CI already includes zero.</t>
+          </r>
         </is>
       </c>
     </row>
@@ -19813,7 +27065,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 3. Share of food-insecure households identified by alternative targeting rules at equal targeting rates, 2025 test set.</t>
+          <t>Table 3. Share of meal-deprived households identified by alternative targeting rules at equal targeting rates, 2025 test set.</t>
         </is>
       </c>
     </row>
@@ -19840,7 +27092,7 @@
       <c r="G3" s="11" t="n"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Targeting rate = FI prevalence (39.3%)</t>
+          <t>Targeting rate = prevalence of meal-affordability deprivation (39.3%)</t>
         </is>
       </c>
     </row>
@@ -20636,7 +27888,7 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Sensitivity: weighted share of food-insecure households selected (95% CI, household bootstrap, 8,000 replicates; intervals conditional on the fitted models). PPV: share of selected households that are food insecure. Children: share of children living in food-insecure households who are selected.</t>
+          <t>Sensitivity: weighted share of meal-deprived households selected (95% CI, household bootstrap, 8,000 replicates; intervals conditional on the fitted models). PPV: share of selected households that are meal-deprived. Children: share of children living in meal-deprived households who are selected.</t>
         </is>
       </c>
     </row>
@@ -20657,7 +27909,7 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Perfect ranking selects food-insecure households first; at a targeting rate below the prevalence its sensitivity equals the targeting rate divided by the prevalence.</t>
+          <t>Perfect ranking selects meal-deprived households first; at a targeting rate below the prevalence its sensitivity equals the targeting rate divided by the prevalence.</t>
         </is>
       </c>
     </row>
@@ -20678,7 +27930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="48.71" customWidth="1" min="1" max="1"/>
@@ -20690,7 +27942,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table S1. Definitions of derived variables.</t>
+          <t>Table S1. Definitions of the outcome, the consumption-frequency and health-cost items, and derived variables.</t>
         </is>
       </c>
     </row>
@@ -20720,22 +27972,22 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Food insecurity (FI)</t>
+          <t>Meal-affordability deprivation</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Household cannot afford a meal with meat, chicken or fish (or vegetarian equivalent) every second day (HE090 = 2)</t>
+          <t>Household cannot afford a meal with meat, chicken or fish, or a vegetarian equivalent, every second day (HE090 = 2). TurkStat codebook wording, identical in 2023–2025: “Haneniz ekonomik olarak; 2 günde bir et, tavuk ya da balık içeren yemeği karşılayabilecek durumda mı? (Vejeteryanlar için eşdeğer yiyecekler)” [Is your household economically able to afford a meal containing meat, chicken or fish every second day? (Equivalent foods for vegetarians)]. Codes 1 = yes, 2 = no; deprived = 2. No recall period: ability to afford at the time of the interview. Missing values: 0 in 2023, 0 in 2024 and 0 in 2025. The household value is assigned to all members.</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>HE090</t>
+          <t>HE090 (TurkStat microdata, household file); EU-SILC target variable HS050 (Capacity to afford a meal with meat, chicken, fish (or vegetarian equivalent) every second day) in Eurostat coding; in the TurkStat files HS050 denotes a different item</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Households; assigned to members</t>
+          <t>Households; household questionnaire, answered for the household by the household respondent; assigned to members</t>
         </is>
       </c>
     </row>
@@ -20791,7 +28043,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Food insecure and not income poor</t>
+          <t>Meal-deprived and not income poor</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -20813,7 +28065,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Weighted share of food-insecure households (persons) that are not identified by a threshold</t>
+          <t>Weighted share of meal-deprived households (persons) that are not identified by a threshold</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -20823,7 +28075,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Food-insecure households (persons)</t>
+          <t>Meal-deprived households (persons)</t>
         </is>
       </c>
     </row>
@@ -21138,66 +28390,66 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Low meat intake</t>
+          <t>Low meat, chicken or fish consumption frequency</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Eats meat, chicken or fish less than once a week (vegetarian or vegan adults excluded; included as low intake in a sensitivity analysis)</t>
+          <t>Eats meat, chicken or fish less than once a week (code 15); vegetarian or vegan adults (code 19) excluded, and counted as low frequency in a sensitivity analysis. TurkStat codebook wording: “Ferdin son 12 ay içerisinde ferdin et, tavuk veya balık yeme sıklığı” [Frequency with which the person ate meat, chicken or fish in the last 12 months]; codes 1 every day, 2 every week (not every day), 15 less than once a week, 19 never, vegetarian or vegan. Recall period: last 12 months. Frequency of consumption; quantities, intake and diet quality not measured.</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>MODUL2_F_5</t>
+          <t>MODUL2_F_5 (2025 energy and environment module, person file)</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Adults ≥18, 2025</t>
+          <t>Adults ≥18 with an individual questionnaire, 2025</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Low fruit intake</t>
+          <t>Low fruit consumption frequency</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Eats fruit less than once a day</t>
+          <t>Eats fruit less than once a day (codes 13, 14, 15, 6). TurkStat codebook wording: “Ferdin olağan/normal bir haftada (7 gün) meyve yeme sıklığı (Konserve veya kuru meyveler dahil olup her çeşit meyve suları hariçtir.)” [Frequency with which the person eats fruit in an ordinary week (7 days); canned or dried fruit included, all fruit juices excluded]; codes 11 twice a day or more, 12 once a day, 13 4–6 times a week, 14 1–3 times a week, 15 less than once a week, 6 never. Recall period: an ordinary week. Frequency of consumption; quantities, intake and diet quality not measured.</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>MODUL1_F_8</t>
+          <t>MODUL1_F_8 (2025 health module, person file)</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Adults ≥18, 2025</t>
+          <t>Adults ≥18 with an individual questionnaire, 2025</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Low vegetable intake</t>
+          <t>Low vegetable consumption frequency</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Eats vegetables or salad less than once a day</t>
+          <t>Eats vegetables or salad less than once a day (codes 13, 14, 15, 6). TurkStat codebook wording: “Ferdin sebze veya salata yeme sıklığı (patates, çorba ve herhangi bir sebze suyu hariç)” [Frequency with which the person eats vegetables or salad, excluding potatoes, soup and any vegetable juice]; codes as for fruit. Recall period: not stated in the codebook (the same daily and weekly response scale as the fruit item, which refers to an ordinary week). Frequency of consumption; quantities, intake and diet quality not measured.</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>MODUL1_F_9</t>
+          <t>MODUL1_F_9 (2025 health module, person file)</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Adults ≥18, 2025</t>
+          <t>Adults ≥18 with an individual questionnaire, 2025</t>
         </is>
       </c>
     </row>
@@ -21209,12 +28461,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Medical examination or treatment costs, or medicine costs, were a heavy burden in the past 12 months</t>
+          <t>Medical examination or treatment costs, or medicine costs, were a heavy burden in the last 12 months (code 1 on either item). TurkStat codebook wording: “Son 12 ay içerisinde hanehalkının tıbbi muayene veya tedaviler için yaptığı tüm harcamaların haneye yük getirme durumu” [Extent to which all household expenditure on medical examinations or treatments in the last 12 months was a burden] and “Son 12 ay içerisinde hanehalkının ilaç için (reçeteli veya reçetesiz) yaptığı tüm masrafların haneye yük getirme durumu” [the same for prescribed or non-prescribed medicines]; codes 1 a heavy burden, 2 somewhat of a burden, 3 not a burden, 4 no such expenditure (counted as not heavily burdened). Recall period: last 12 months.</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>MODUL1_H_1, MODUL1_H_3</t>
+          <t>MODUL1_H_1, MODUL1_H_3 (2025 health module, household file)</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -21253,7 +28505,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>G1 food secure; G2 food insecure, not poor; G3 food insecure and poor</t>
+          <t>G1 not meal-deprived; G2 meal-deprived, not poor; G3 meal-deprived and poor</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -21264,6 +28516,13 @@
       <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Households and adults, 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>Turkish wording: TurkStat micro data codebooks (variable lists of the household, person and 2025 module files); no questionnaire was available, so the codebook wording is quoted. English translations by the authors. HS050 is the EU-SILC target-variable code in Eurostat's documentation; the TurkStat files use their own codes.</t>
         </is>
       </c>
     </row>
@@ -22837,7 +30096,7 @@
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>T4 Deprivation items (upper bound only)</t>
+          <t>T4 Other deprivation items, same battery as the outcome (upper bound only)</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr"/>
@@ -24296,7 +31555,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Food insecurity (HE090)</t>
+          <t>Meal-affordability deprivation (HE090)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -25937,7 +33196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="48.71" customWidth="1" min="1" max="1"/>
@@ -25947,6 +33206,7 @@
     <col width="16.71" customWidth="1" min="5" max="5"/>
     <col width="16.71" customWidth="1" min="6" max="6"/>
     <col width="16.71" customWidth="1" min="7" max="7"/>
+    <col width="16.71" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25980,15 +33240,20 @@
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
+          <t>2025 main test set, calibrated weights</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
           <t>2025, matched (excluded from testing)</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>2025, all</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>SMD, main test vs development</t>
         </is>
@@ -26017,20 +33282,25 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
+          <t>7,861</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
           <t>17,975</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>25,836</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Food-insecure households, n</t>
+          <t>Meal-deprived households, n</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -26050,20 +33320,25 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
+          <t>3,257</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
           <t>6,807</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>10,064</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Food insecure, %</t>
+          <t>Meal-deprived, %</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -26083,15 +33358,20 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
+          <t>38.3</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
           <t>35.9</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>37.0</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>0.03</t>
         </is>
@@ -26120,15 +33400,20 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
           <t>16.2</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>16.0</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>−0.03</t>
         </is>
@@ -26157,15 +33442,20 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
           <t>16.9</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>19.9</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>0.17</t>
         </is>
@@ -26194,15 +33484,20 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
+          <t>41.2</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
           <t>42.5</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>41.2</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>−0.09</t>
         </is>
@@ -26231,15 +33526,20 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
           <t>26.9</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>26.0</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>−0.03</t>
         </is>
@@ -26268,15 +33568,20 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>−0.13</t>
         </is>
@@ -26310,10 +33615,15 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
           <t>1.10</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>0.03</t>
         </is>
@@ -26342,15 +33652,20 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
+          <t>51.0</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
           <t>51.9</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>51.2</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>−0.07</t>
         </is>
@@ -26379,15 +33694,20 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
+          <t>27.5</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
           <t>26.6</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>27.4</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
@@ -26416,15 +33736,20 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
+          <t>22.5</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
           <t>22.1</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>22.9</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>0.06</t>
         </is>
@@ -26453,15 +33778,20 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
+          <t>55.4</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
           <t>56.2</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>55.4</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>−0.01</t>
         </is>
@@ -26490,15 +33820,20 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
+          <t>28.2</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
           <t>27.2</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>28.2</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>0.03</t>
         </is>
@@ -26527,15 +33862,20 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
+          <t>49.0</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>49.2</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>0.04</t>
         </is>
@@ -26564,15 +33904,20 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
           <t>26.9</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>26.8</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>−0.06</t>
         </is>
@@ -26601,15 +33946,20 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
+          <t>18.6</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
           <t>18.3</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>18.6</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
@@ -26632,7 +33982,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Signature-only cleaned test set (sensitivity analysis): 12,241 households (49.1% of weighted households; 40.5% one-person, weighted; food insecure 40.1%, poor 14.7%).</t>
+          <t>Signature-only cleaned test set (sensitivity analysis): 12,241 households (49.1% of weighted households; 40.5% one-person, weighted; meal-deprived 40.1%, poor 14.7%).</t>
         </is>
       </c>
     </row>
